--- a/data/gravel/Stanton Sherpa Ti 2025.xlsx
+++ b/data/gravel/Stanton Sherpa Ti 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE95660-984B-B94B-A83A-D3B6CC3844E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC037DB-0663-E445-ABA0-732D13B15717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33300" yWindow="-26680" windowWidth="27940" windowHeight="24100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -351,6 +351,9 @@
   </si>
   <si>
     <t>not specified. Fox 120 fork. My estimate is 43.5</t>
+  </si>
+  <si>
+    <t>https://www.stantonbikes.com/cdn/shop/files/sherpa_ti_small_file.jpg?v=1676454879&amp;width=1920</t>
   </si>
 </sst>
 </file>
@@ -740,6 +743,11 @@
         <v>103</v>
       </c>
     </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>106</v>
+      </c>
+    </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Stanton Sherpa Ti 2025.xlsx
+++ b/data/gravel/Stanton Sherpa Ti 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC037DB-0663-E445-ABA0-732D13B15717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E528AA-4599-874D-9218-26B58A3AAAA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33300" yWindow="-26680" windowWidth="27940" windowHeight="24100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10060" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -354,6 +354,12 @@
   </si>
   <si>
     <t>https://www.stantonbikes.com/cdn/shop/files/sherpa_ti_small_file.jpg?v=1676454879&amp;width=1920</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Matlock, Derbyshire, United Kingdom</t>
   </si>
 </sst>
 </file>
@@ -697,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1388,6 +1394,14 @@
         <v>77</v>
       </c>
     </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>107</v>
+      </c>
+      <c r="B73" t="s">
+        <v>108</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Stanton Sherpa Ti 2025.xlsx
+++ b/data/gravel/Stanton Sherpa Ti 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7E528AA-4599-874D-9218-26B58A3AAAA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F69B71B-FBF0-1946-8E8B-0B72D22CE8F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10060" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -263,9 +263,6 @@
     <t>Chainstay Length (mm)</t>
   </si>
   <si>
-    <t>steel</t>
-  </si>
-  <si>
     <t>USD</t>
   </si>
   <si>
@@ -360,6 +357,9 @@
   </si>
   <si>
     <t>Matlock, Derbyshire, United Kingdom</t>
+  </si>
+  <si>
+    <t>titanium</t>
   </si>
 </sst>
 </file>
@@ -714,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -746,12 +746,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -759,7 +759,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -767,16 +767,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" t="s">
         <v>87</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>88</v>
-      </c>
-      <c r="E8" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -818,7 +818,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C11">
         <v>600</v>
@@ -832,10 +832,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C12">
         <v>586.39</v>
@@ -852,7 +852,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C13">
         <v>430</v>
@@ -886,7 +886,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C15">
         <v>1151.06</v>
@@ -903,7 +903,7 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16">
         <v>56</v>
@@ -920,7 +920,7 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -971,7 +971,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -983,7 +983,7 @@
         <v>500</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G20" s="1"/>
     </row>
@@ -992,7 +992,7 @@
         <v>18</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G21">
         <v>530</v>
@@ -1003,7 +1003,7 @@
         <v>17</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G22">
         <v>500</v>
@@ -1026,7 +1026,7 @@
         <v>44</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -1147,7 +1147,7 @@
         <v>67</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -1155,7 +1155,7 @@
         <v>68</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -1163,7 +1163,7 @@
         <v>69</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -1171,7 +1171,7 @@
         <v>32</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -1234,7 +1234,7 @@
         <v>41</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
@@ -1247,7 +1247,7 @@
         <v>43</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -1299,7 +1299,7 @@
         <v>52</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -1307,7 +1307,7 @@
         <v>53</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -1372,7 +1372,7 @@
         <v>2280</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -1391,15 +1391,15 @@
         <v>66</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>106</v>
+      </c>
+      <c r="B73" t="s">
         <v>107</v>
-      </c>
-      <c r="B73" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Stanton Sherpa Ti 2025.xlsx
+++ b/data/gravel/Stanton Sherpa Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F69B71B-FBF0-1946-8E8B-0B72D22CE8F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E16ECE-FC39-054B-B2EA-E3094FD9E8E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -360,6 +360,24 @@
   </si>
   <si>
     <t>titanium</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -703,7 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1244,161 +1262,191 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>44</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51">
-        <v>31.6</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>46</v>
-      </c>
-      <c r="B52" s="1"/>
+        <v>112</v>
+      </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>48</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>43</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="B57">
+        <v>31.6</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>52</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>94</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="B58" s="1"/>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>53</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>54</v>
-      </c>
-      <c r="B60" s="1"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>56</v>
-      </c>
-      <c r="B62">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>58</v>
-      </c>
-      <c r="B64" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>59</v>
-      </c>
-      <c r="B65" s="1"/>
+        <v>53</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B66" s="1"/>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>61</v>
-      </c>
-      <c r="B67" s="1"/>
+        <v>55</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>62</v>
-      </c>
-      <c r="B68" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
+      </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>63</v>
-      </c>
-      <c r="B69">
-        <v>2280</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>64</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B70" s="1"/>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B71" s="1"/>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>66</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>76</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B72" s="1"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>61</v>
+      </c>
+      <c r="B73" s="1"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74" s="1"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75">
+        <v>2280</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>65</v>
+      </c>
+      <c r="B77" s="1"/>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>66</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>106</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>107</v>
       </c>
     </row>

--- a/data/gravel/Stanton Sherpa Ti 2025.xlsx
+++ b/data/gravel/Stanton Sherpa Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E16ECE-FC39-054B-B2EA-E3094FD9E8E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD14E8B-41DC-4346-B300-4E1DFB13165B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="118">
   <si>
     <t>brand</t>
   </si>
@@ -332,9 +332,6 @@
     <t>Axle to Crown (mm) used for above measurements</t>
   </si>
   <si>
-    <t>height used for above measurements</t>
-  </si>
-  <si>
     <t>axle crown</t>
   </si>
   <si>
@@ -344,9 +341,6 @@
     <t>https://www.stantonbikes.com/collections/sherpa-ti</t>
   </si>
   <si>
-    <t>a8:e32</t>
-  </si>
-  <si>
     <t>not specified. Fox 120 fork. My estimate is 43.5</t>
   </si>
   <si>
@@ -378,6 +372,21 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>"height used for above measurements"</t>
+  </si>
+  <si>
+    <t>100-130</t>
+  </si>
+  <si>
+    <t>a8:e34</t>
   </si>
 </sst>
 </file>
@@ -721,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -764,12 +773,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -777,7 +786,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -933,7 +942,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -950,7 +959,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -967,7 +976,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -984,7 +993,7 @@
         <v>75.5</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -1001,33 +1010,33 @@
         <v>500</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G21">
         <v>530</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G22">
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -1044,410 +1053,431 @@
         <v>44</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C24">
+        <v>120</v>
+      </c>
+      <c r="D24">
+        <v>120</v>
+      </c>
+      <c r="E24">
+        <v>120</v>
+      </c>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G25" s="1"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>24</v>
       </c>
-      <c r="C27">
+      <c r="C29">
         <v>1940</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>25</v>
       </c>
-      <c r="C28">
+      <c r="C30">
         <v>700</v>
       </c>
-      <c r="D28">
+      <c r="D30">
         <v>700</v>
       </c>
-      <c r="E28">
+      <c r="E30">
         <v>700</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>26</v>
       </c>
-      <c r="C29">
+      <c r="C31">
         <v>2.4</v>
       </c>
-      <c r="D29">
+      <c r="D31">
         <v>2.4</v>
       </c>
-      <c r="E29">
+      <c r="E31">
         <v>2.4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>27</v>
       </c>
-      <c r="C30">
+      <c r="C32">
         <v>2.5</v>
       </c>
-      <c r="D30">
+      <c r="D32">
         <v>2.5</v>
       </c>
-      <c r="E30">
+      <c r="E32">
         <v>2.5</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>28</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B33" t="s">
         <v>28</v>
       </c>
-      <c r="C31">
+      <c r="C33">
         <v>165</v>
       </c>
-      <c r="D31">
+      <c r="D33">
         <v>178</v>
       </c>
-      <c r="E31">
+      <c r="E33">
         <v>188</v>
       </c>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>29</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B34" t="s">
         <v>29</v>
       </c>
-      <c r="C32">
+      <c r="C34">
         <v>178</v>
       </c>
-      <c r="D32">
+      <c r="D34">
         <v>188</v>
       </c>
-      <c r="E32">
+      <c r="E34">
         <v>193</v>
       </c>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>30</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B36" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
         <v>67</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>69</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+      <c r="B40" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>33</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>35</v>
       </c>
-      <c r="B41">
+      <c r="B43">
         <v>2.5</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>36</v>
       </c>
-      <c r="B42">
+      <c r="B44">
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>37</v>
       </c>
-      <c r="B43">
+      <c r="B45" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46">
         <v>120</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>109</v>
+        <v>41</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>110</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>44</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>45</v>
-      </c>
-      <c r="B57">
-        <v>31.6</v>
+        <v>43</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>46</v>
-      </c>
-      <c r="B58" s="1"/>
+        <v>44</v>
+      </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>47</v>
+        <v>45</v>
+      </c>
+      <c r="B59">
+        <v>31.6</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>48</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="B60" s="1"/>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>52</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>53</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>54</v>
-      </c>
-      <c r="B66" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>55</v>
+        <v>53</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>56</v>
-      </c>
-      <c r="B68">
-        <v>2</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B68" s="1"/>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>58</v>
-      </c>
-      <c r="B70" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
+      </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>59</v>
-      </c>
-      <c r="B71" s="1"/>
+        <v>57</v>
+      </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B72" s="1"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B73" s="1"/>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B74" s="1"/>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>63</v>
-      </c>
-      <c r="B75">
-        <v>2280</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>83</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B75" s="1"/>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>64</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="B76" s="1"/>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>65</v>
-      </c>
-      <c r="B77" s="1"/>
+        <v>63</v>
+      </c>
+      <c r="B77">
+        <v>2280</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>66</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>106</v>
-      </c>
-      <c r="B79" t="s">
-        <v>107</v>
+        <v>65</v>
+      </c>
+      <c r="B79" s="1"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>66</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>104</v>
+      </c>
+      <c r="B81" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Stanton Sherpa Ti 2025.xlsx
+++ b/data/gravel/Stanton Sherpa Ti 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD14E8B-41DC-4346-B300-4E1DFB13165B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E8038A-3E3F-3342-A236-DAB7A1CDA474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6320" yWindow="1460" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="123">
   <si>
     <t>brand</t>
   </si>
@@ -332,21 +332,6 @@
     <t>Axle to Crown (mm) used for above measurements</t>
   </si>
   <si>
-    <t>axle crown</t>
-  </si>
-  <si>
-    <t>25% sag</t>
-  </si>
-  <si>
-    <t>https://www.stantonbikes.com/collections/sherpa-ti</t>
-  </si>
-  <si>
-    <t>not specified. Fox 120 fork. My estimate is 43.5</t>
-  </si>
-  <si>
-    <t>https://www.stantonbikes.com/cdn/shop/files/sherpa_ti_small_file.jpg?v=1676454879&amp;width=1920</t>
-  </si>
-  <si>
     <t>location</t>
   </si>
   <si>
@@ -380,13 +365,43 @@
     <t>fork_sag</t>
   </si>
   <si>
-    <t>"height used for above measurements"</t>
-  </si>
-  <si>
     <t>100-130</t>
   </si>
   <si>
-    <t>a8:e34</t>
+    <t>travel</t>
+  </si>
+  <si>
+    <t>20% + 15</t>
+  </si>
+  <si>
+    <t>30% + 15</t>
+  </si>
+  <si>
+    <t>I think this means that the fork ac + 15 is the length from axle to head tube</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>15"</t>
+  </si>
+  <si>
+    <t>Head Tube Angle</t>
+  </si>
+  <si>
+    <t>Seat Tube Angle</t>
+  </si>
+  <si>
+    <t>Axle to Crown (mm) (15mm bottom cup)</t>
+  </si>
+  <si>
+    <t>a8:f34</t>
+  </si>
+  <si>
+    <t>https://www.stantonbikes.com/collections/sherpa-ti-gen4</t>
+  </si>
+  <si>
+    <t>https://www.stantonbikes.com/cdn/shop/files/sherpa_ti_hero_b098c17f-cdcb-45b4-87d9-678cdce2138f.jpg?v=1714561126&amp;width=2400</t>
   </si>
 </sst>
 </file>
@@ -429,11 +444,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -730,13 +747,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -744,7 +761,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -752,7 +769,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -760,53 +777,71 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>45938</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>45997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+      <c r="J7" s="2">
+        <v>45938</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J8" t="s">
         <v>97</v>
       </c>
-      <c r="C8" t="s">
+      <c r="K8" t="s">
         <v>86</v>
       </c>
-      <c r="D8" t="s">
+      <c r="L8" t="s">
         <v>87</v>
       </c>
-      <c r="E8" t="s">
+      <c r="M8" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -814,16 +849,31 @@
         <v>73</v>
       </c>
       <c r="C9">
+        <v>604</v>
+      </c>
+      <c r="D9">
+        <v>604</v>
+      </c>
+      <c r="E9">
+        <v>623</v>
+      </c>
+      <c r="F9">
+        <v>642</v>
+      </c>
+      <c r="J9" t="s">
+        <v>73</v>
+      </c>
+      <c r="K9">
         <v>599.99</v>
       </c>
-      <c r="D9">
+      <c r="L9">
         <v>618.4</v>
       </c>
-      <c r="E9">
+      <c r="M9">
         <v>636.80999999999995</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -831,16 +881,31 @@
         <v>74</v>
       </c>
       <c r="C10">
+        <v>444</v>
+      </c>
+      <c r="D10">
+        <v>468</v>
+      </c>
+      <c r="E10">
+        <v>495</v>
+      </c>
+      <c r="F10">
+        <v>509</v>
+      </c>
+      <c r="J10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K10">
         <v>440.99</v>
       </c>
-      <c r="D10">
+      <c r="L10">
         <v>461.22</v>
       </c>
-      <c r="E10">
+      <c r="M10">
         <v>481.46</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -856,8 +921,23 @@
       <c r="E11">
         <v>650</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11">
+        <v>675</v>
+      </c>
+      <c r="J11" t="s">
+        <v>89</v>
+      </c>
+      <c r="K11">
+        <v>600</v>
+      </c>
+      <c r="L11">
+        <v>625</v>
+      </c>
+      <c r="M11">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>93</v>
       </c>
@@ -865,16 +945,31 @@
         <v>90</v>
       </c>
       <c r="C12">
+        <v>600</v>
+      </c>
+      <c r="D12">
+        <v>613</v>
+      </c>
+      <c r="E12">
+        <v>636</v>
+      </c>
+      <c r="F12">
+        <v>658</v>
+      </c>
+      <c r="J12" t="s">
+        <v>90</v>
+      </c>
+      <c r="K12">
         <v>586.39</v>
       </c>
-      <c r="D12">
+      <c r="L12">
         <v>606.36</v>
       </c>
-      <c r="E12">
+      <c r="M12">
         <v>629.29999999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -882,16 +977,31 @@
         <v>91</v>
       </c>
       <c r="C13">
+        <v>381</v>
+      </c>
+      <c r="D13">
         <v>430</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>482</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>533</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="J13" t="s">
+        <v>91</v>
+      </c>
+      <c r="K13">
+        <v>430</v>
+      </c>
+      <c r="L13">
+        <v>482</v>
+      </c>
+      <c r="M13">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -907,8 +1017,23 @@
       <c r="E14">
         <v>435</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F14">
+        <v>435</v>
+      </c>
+      <c r="J14" t="s">
+        <v>75</v>
+      </c>
+      <c r="K14">
+        <v>435</v>
+      </c>
+      <c r="L14">
+        <v>435</v>
+      </c>
+      <c r="M14">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -916,16 +1041,31 @@
         <v>78</v>
       </c>
       <c r="C15">
+        <v>1150</v>
+      </c>
+      <c r="D15">
+        <v>1175</v>
+      </c>
+      <c r="E15">
+        <v>1210</v>
+      </c>
+      <c r="F15">
+        <v>1230</v>
+      </c>
+      <c r="J15" t="s">
+        <v>78</v>
+      </c>
+      <c r="K15">
         <v>1151.06</v>
       </c>
-      <c r="D15">
+      <c r="L15">
         <v>1178.33</v>
       </c>
-      <c r="E15">
+      <c r="M15">
         <v>1206.6099999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -933,16 +1073,31 @@
         <v>92</v>
       </c>
       <c r="C16">
+        <v>58</v>
+      </c>
+      <c r="D16">
+        <v>58</v>
+      </c>
+      <c r="E16">
+        <v>58</v>
+      </c>
+      <c r="F16">
+        <v>58</v>
+      </c>
+      <c r="J16" t="s">
+        <v>92</v>
+      </c>
+      <c r="K16">
         <v>56</v>
       </c>
-      <c r="D16">
+      <c r="L16">
         <v>56</v>
       </c>
-      <c r="E16">
+      <c r="M16">
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -953,18 +1108,33 @@
         <v>100</v>
       </c>
       <c r="D17">
+        <v>100</v>
+      </c>
+      <c r="E17">
         <v>120</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>140</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="J17" t="s">
+        <v>77</v>
+      </c>
+      <c r="K17">
+        <v>100</v>
+      </c>
+      <c r="L17">
+        <v>120</v>
+      </c>
+      <c r="M17">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="C18">
         <v>67</v>
@@ -975,13 +1145,28 @@
       <c r="E18">
         <v>67</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F18">
+        <v>67</v>
+      </c>
+      <c r="J18" t="s">
+        <v>71</v>
+      </c>
+      <c r="K18">
+        <v>67</v>
+      </c>
+      <c r="L18">
+        <v>67</v>
+      </c>
+      <c r="M18">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="C19">
         <v>75.5</v>
@@ -992,13 +1177,28 @@
       <c r="E19">
         <v>75.5</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F19">
+        <v>75.5</v>
+      </c>
+      <c r="J19" t="s">
+        <v>72</v>
+      </c>
+      <c r="K19">
+        <v>75.5</v>
+      </c>
+      <c r="L19">
+        <v>75.5</v>
+      </c>
+      <c r="M19">
+        <v>75.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>98</v>
+      <c r="B20" t="s">
+        <v>119</v>
       </c>
       <c r="C20">
         <v>500</v>
@@ -1009,34 +1209,56 @@
       <c r="E20">
         <v>500</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F20">
+        <v>500</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J20" t="s">
+        <v>98</v>
+      </c>
+      <c r="K20">
+        <v>500</v>
+      </c>
+      <c r="L20">
+        <v>500</v>
+      </c>
+      <c r="M20">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G21">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G21" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H21">
+        <v>100</v>
+      </c>
+      <c r="I21">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G22">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G22" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="H22">
+        <f>505-$G22*H$21</f>
+        <v>485</v>
+      </c>
+      <c r="I22">
+        <f>530-$G22*I$21</f>
+        <v>506</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -1053,54 +1275,86 @@
         <v>44</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+      <c r="H23">
+        <f>H22+15</f>
+        <v>500</v>
+      </c>
+      <c r="I23">
+        <f>I22+15</f>
+        <v>521</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24">
+        <v>100</v>
+      </c>
+      <c r="D24">
+        <v>100</v>
+      </c>
+      <c r="E24">
+        <v>100</v>
+      </c>
+      <c r="F24">
+        <v>100</v>
+      </c>
+      <c r="G24" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="H24">
+        <f>505-$G24*H$21</f>
+        <v>475</v>
+      </c>
+      <c r="I24">
+        <f>530-$G24*I$21</f>
+        <v>494</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C24">
-        <v>120</v>
-      </c>
-      <c r="D24">
-        <v>120</v>
-      </c>
-      <c r="E24">
-        <v>120</v>
-      </c>
-      <c r="G24" s="1"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="G25" s="1"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H25">
+        <f>H24+15</f>
+        <v>490</v>
+      </c>
+      <c r="I25">
+        <f>I24+15</f>
+        <v>509</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>24</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>1940</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -1113,8 +1367,11 @@
       <c r="E30">
         <v>700</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F30">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -1127,8 +1384,11 @@
       <c r="E31">
         <v>2.4</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F31">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -1139,6 +1399,9 @@
         <v>2.5</v>
       </c>
       <c r="E32">
+        <v>2.5</v>
+      </c>
+      <c r="F32">
         <v>2.5</v>
       </c>
     </row>
@@ -1150,13 +1413,16 @@
         <v>28</v>
       </c>
       <c r="C33">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D33">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E33">
-        <v>188</v>
+        <v>180</v>
+      </c>
+      <c r="F33">
+        <v>190</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
@@ -1170,12 +1436,15 @@
         <v>29</v>
       </c>
       <c r="C34">
+        <v>170</v>
+      </c>
+      <c r="D34">
         <v>178</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>188</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>193</v>
       </c>
       <c r="G34" s="3"/>
@@ -1219,7 +1488,7 @@
         <v>32</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
@@ -1256,7 +1525,7 @@
         <v>37</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
@@ -1264,7 +1533,7 @@
         <v>38</v>
       </c>
       <c r="B46">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
@@ -1292,32 +1561,32 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -1447,7 +1716,7 @@
         <v>63</v>
       </c>
       <c r="B77">
-        <v>2280</v>
+        <v>2266</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>83</v>
@@ -1474,10 +1743,10 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B81" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
